--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.3.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.3.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.22250.3" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="oocihm.22250.3" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -581,19 +581,15 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.3.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.3.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0003.txt</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t>L53: possible duplicated/overlap line with previous line (similarity 89%) :: Pages restored and / or laminated /</t>
-        </is>
-      </c>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0003.txt</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr"/>
       <c r="E2" s="1" t="inlineStr"/>
       <c r="F2" s="1" t="inlineStr"/>
       <c r="G2" s="1" t="inlineStr"/>
@@ -660,11 +656,7 @@
           <t>186</t>
         </is>
       </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>L56: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | possible duplicated/overlap line with previous line (similarity 79%) :: Pages restaur Ã© es et / ou pellicul Ã© es</t>
-        </is>
-      </c>
+      <c r="D3" s="1" t="inlineStr"/>
       <c r="E3" s="1" t="inlineStr"/>
       <c r="F3" s="1" t="inlineStr"/>
       <c r="G3" s="1" t="inlineStr"/>
@@ -731,11 +723,7 @@
           <t>443</t>
         </is>
       </c>
-      <c r="D4" s="1" t="inlineStr">
-        <is>
-          <t>L173: possible duplicated/overlap line with previous line (similarity 89%) :: Pages restored and / or laminated /</t>
-        </is>
-      </c>
+      <c r="D4" s="1" t="inlineStr"/>
       <c r="E4" s="1" t="inlineStr"/>
       <c r="F4" s="1" t="inlineStr"/>
       <c r="G4" s="1" t="inlineStr"/>
@@ -790,7 +778,7 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>75</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
@@ -798,11 +786,7 @@
           <t>52</t>
         </is>
       </c>
-      <c r="D5" s="1" t="inlineStr">
-        <is>
-          <t>L175: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | possible duplicated/overlap line with previous line (similarity 79%) :: Pages restaur Ã© es et / ou pellicul Ã© es</t>
-        </is>
-      </c>
+      <c r="D5" s="1" t="inlineStr"/>
       <c r="E5" s="1" t="inlineStr"/>
       <c r="F5" s="1" t="inlineStr"/>
       <c r="G5" s="1" t="inlineStr"/>
@@ -915,12 +899,12 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C7" s="1" t="inlineStr">
@@ -944,7 +928,7 @@
       </c>
       <c r="J7" s="1" t="inlineStr">
         <is>
-          <t>L56: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | possible duplicated/overlap line with previous line (similarity 79%) :: Pages restaur Ã© es et / ou pellicul Ã© es</t>
+          <t>L56: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Pages restaur Ã© es et / ou pellicul Ã© es</t>
         </is>
       </c>
       <c r="K7" s="1" t="inlineStr">
@@ -2211,7 +2195,7 @@
       <c r="I36" s="1" t="inlineStr"/>
       <c r="J36" s="1" t="inlineStr">
         <is>
-          <t>L175: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | possible duplicated/overlap line with previous line (similarity 79%) :: Pages restaur Ã© es et / ou pellicul Ã© es</t>
+          <t>L175: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Pages restaur Ã© es et / ou pellicul Ã© es</t>
         </is>
       </c>
       <c r="K36" s="1" t="inlineStr"/>

--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.3.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.3.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="oocihm.22250.3" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.22250.3" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -416,22 +416,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y41"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
     <col width="58" customWidth="1" min="9" max="9"/>
-    <col width="60" customWidth="1" min="10" max="10"/>
+    <col width="27" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="40" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
@@ -603,18 +603,18 @@
           <t>L155: suspicious token(s): 10X (letter/digit mix) :: 10X</t>
         </is>
       </c>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t>L2: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Ce document est film Ã© au taux de r Ã© duction indiqu Ã© ci-dessous.</t>
-        </is>
-      </c>
+      <c r="J2" s="1" t="inlineStr"/>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L17: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: L'institut a microfilmÃ© le meilleur exemplaire</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L21: isolated marker/symbol line :: "</t>
@@ -622,7 +622,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L1: isolated marker/symbol line :: ï»¿</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr"/>
@@ -653,7 +653,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>123</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -670,14 +670,10 @@
           <t>L157: suspicious token(s): 14X (letter/digit mix) :: 14X</t>
         </is>
       </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>L10: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Ce document est film Ã© au taux de r Ã© duction indiqu Ã© ci-dessous.</t>
-        </is>
-      </c>
+      <c r="J3" s="1" t="inlineStr"/>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L18: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: qu'il lui a Ã©tÃ© possible de se procurer. Les dÃ©tails</t>
+          <t>L122: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -737,14 +733,10 @@
           <t>L159: suspicious token(s): 18X (letter/digit mix) :: 18X</t>
         </is>
       </c>
-      <c r="J4" s="1" t="inlineStr">
-        <is>
-          <t>L24: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: qu'il lui a Ã© te possible de se procurer. Les d Ã© tails</t>
-        </is>
-      </c>
+      <c r="J4" s="1" t="inlineStr"/>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L22: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: modification dans la mÃ©thode normale de filmage</t>
+          <t>L169: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
@@ -778,12 +770,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>29</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -800,16 +792,8 @@
           <t>L161: suspicious token(s): 22X (letter/digit mix) :: 22X</t>
         </is>
       </c>
-      <c r="J5" s="1" t="inlineStr">
-        <is>
-          <t>L26: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: de cet exemplaire qui sont peut- Ã¨ tre uniques du</t>
-        </is>
-      </c>
-      <c r="K5" s="1" t="inlineStr">
-        <is>
-          <t>L23: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: sont indiquÃ©s ci-dessous.</t>
-        </is>
-      </c>
+      <c r="J5" s="1" t="inlineStr"/>
+      <c r="K5" s="1" t="inlineStr"/>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr">
@@ -863,16 +847,8 @@
           <t>L163: suspicious token(s): 26X (letter/digit mix) :: 26X</t>
         </is>
       </c>
-      <c r="J6" s="1" t="inlineStr">
-        <is>
-          <t>L55: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Couverture restaur Ã© e et / ou pellicul Ã© e</t>
-        </is>
-      </c>
-      <c r="K6" s="1" t="inlineStr">
-        <is>
-          <t>L53: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Couverture endommagÃ©e.</t>
-        </is>
-      </c>
+      <c r="J6" s="1" t="inlineStr"/>
+      <c r="K6" s="1" t="inlineStr"/>
       <c r="L6" s="1" t="inlineStr"/>
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr">
@@ -926,16 +902,8 @@
           <t>L165: suspicious token(s): 30X (letter/digit mix) :: 30X</t>
         </is>
       </c>
-      <c r="J7" s="1" t="inlineStr">
-        <is>
-          <t>L56: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Pages restaur Ã© es et / ou pellicul Ã© es</t>
-        </is>
-      </c>
-      <c r="K7" s="1" t="inlineStr">
-        <is>
-          <t>L56: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Pages endommagÃ©es</t>
-        </is>
-      </c>
+      <c r="J7" s="1" t="inlineStr"/>
+      <c r="K7" s="1" t="inlineStr"/>
       <c r="L7" s="1" t="inlineStr"/>
       <c r="M7" s="1" t="inlineStr"/>
       <c r="N7" s="1" t="inlineStr">
@@ -989,16 +957,8 @@
           <t>L171: suspicious token(s): 12X (letter/digit mix) :: 12X</t>
         </is>
       </c>
-      <c r="J8" s="1" t="inlineStr">
-        <is>
-          <t>L63: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Pages d Ã© scolor Ã© es, tachet Ã© es ou piqu Ã© es</t>
-        </is>
-      </c>
-      <c r="K8" s="1" t="inlineStr">
-        <is>
-          <t>L59: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Couverture restaurÃ©e et/ou pelliculÃ©e</t>
-        </is>
-      </c>
+      <c r="J8" s="1" t="inlineStr"/>
+      <c r="K8" s="1" t="inlineStr"/>
       <c r="L8" s="1" t="inlineStr"/>
       <c r="M8" s="1" t="inlineStr"/>
       <c r="N8" s="1" t="inlineStr">
@@ -1052,16 +1012,8 @@
           <t>L173: suspicious token(s): 16X (letter/digit mix) :: 16X</t>
         </is>
       </c>
-      <c r="J9" s="1" t="inlineStr">
-        <is>
-          <t>L66: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Cartes g Ã© ographiques en couleur</t>
-        </is>
-      </c>
-      <c r="K9" s="1" t="inlineStr">
-        <is>
-          <t>L62: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Pages restaurÃ©es et/ou pelliculÃ©es</t>
-        </is>
-      </c>
+      <c r="J9" s="1" t="inlineStr"/>
+      <c r="K9" s="1" t="inlineStr"/>
       <c r="L9" s="1" t="inlineStr"/>
       <c r="M9" s="1" t="inlineStr"/>
       <c r="N9" s="1" t="inlineStr">
@@ -1071,7 +1023,7 @@
       </c>
       <c r="O9" s="1" t="inlineStr">
         <is>
-          <t>L122: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L122: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P9" s="1" t="inlineStr"/>
@@ -1093,12 +1045,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1115,16 +1067,8 @@
           <t>L175: suspicious token(s): 20X (letter/digit mix) :: 20X</t>
         </is>
       </c>
-      <c r="J10" s="1" t="inlineStr">
-        <is>
-          <t>L67: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Pages d Ã© tach Ã© es</t>
-        </is>
-      </c>
-      <c r="K10" s="1" t="inlineStr">
-        <is>
-          <t>L69: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Cartes gÃ©ographiques en couleur</t>
-        </is>
-      </c>
+      <c r="J10" s="1" t="inlineStr"/>
+      <c r="K10" s="1" t="inlineStr"/>
       <c r="L10" s="1" t="inlineStr"/>
       <c r="M10" s="1" t="inlineStr"/>
       <c r="N10" s="1" t="inlineStr">
@@ -1161,7 +1105,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1178,16 +1122,8 @@
           <t>L177: suspicious token(s): 24X (letter/digit mix) :: 24X</t>
         </is>
       </c>
-      <c r="J11" s="1" t="inlineStr">
-        <is>
-          <t>L80: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Qualit Ã© in Ã© gale de I'impression</t>
-        </is>
-      </c>
-      <c r="K11" s="1" t="inlineStr">
-        <is>
-          <t>L72: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Pages dÃ©colorÃ©es, tachetÃ©es ou piquÃ©es</t>
-        </is>
-      </c>
+      <c r="J11" s="1" t="inlineStr"/>
+      <c r="K11" s="1" t="inlineStr"/>
       <c r="L11" s="1" t="inlineStr"/>
       <c r="M11" s="1" t="inlineStr"/>
       <c r="N11" s="1" t="inlineStr">
@@ -1241,16 +1177,8 @@
           <t>L179: suspicious token(s): 28X (letter/digit mix) :: 28X</t>
         </is>
       </c>
-      <c r="J12" s="1" t="inlineStr">
-        <is>
-          <t>L86: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Reli Ã© avec d'autres documents</t>
-        </is>
-      </c>
-      <c r="K12" s="1" t="inlineStr">
-        <is>
-          <t>L76: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Pages dÃ©tachÃ©es</t>
-        </is>
-      </c>
+      <c r="J12" s="1" t="inlineStr"/>
+      <c r="K12" s="1" t="inlineStr"/>
       <c r="L12" s="1" t="inlineStr"/>
       <c r="M12" s="1" t="inlineStr"/>
       <c r="N12" s="1" t="inlineStr">
@@ -1304,16 +1232,8 @@
           <t>L181: suspicious token(s): 32X (letter/digit mix) :: 32X</t>
         </is>
       </c>
-      <c r="J13" s="1" t="inlineStr">
-        <is>
-          <t>L87: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Comprend du mat Ã© brie suppl Ã© mentaire</t>
-        </is>
-      </c>
-      <c r="K13" s="1" t="inlineStr">
-        <is>
-          <t>L95: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: QualitÃ© inÃ©gale de l'impression</t>
-        </is>
-      </c>
+      <c r="J13" s="1" t="inlineStr"/>
+      <c r="K13" s="1" t="inlineStr"/>
       <c r="L13" s="1" t="inlineStr"/>
       <c r="M13" s="1" t="inlineStr"/>
       <c r="N13" s="1" t="inlineStr">
@@ -1363,16 +1283,8 @@
         </is>
       </c>
       <c r="I14" s="1" t="inlineStr"/>
-      <c r="J14" s="1" t="inlineStr">
-        <is>
-          <t>L95: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Seule Ã© dition disponible</t>
-        </is>
-      </c>
-      <c r="K14" s="1" t="inlineStr">
-        <is>
-          <t>L106: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: ReliÃ© avec d'autres documents</t>
-        </is>
-      </c>
+      <c r="J14" s="1" t="inlineStr"/>
+      <c r="K14" s="1" t="inlineStr"/>
       <c r="L14" s="1" t="inlineStr"/>
       <c r="M14" s="1" t="inlineStr"/>
       <c r="N14" s="1" t="inlineStr">
@@ -1382,7 +1294,7 @@
       </c>
       <c r="O14" s="1" t="inlineStr">
         <is>
-          <t>L169: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L169: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P14" s="1" t="inlineStr"/>
@@ -1422,16 +1334,8 @@
         </is>
       </c>
       <c r="I15" s="1" t="inlineStr"/>
-      <c r="J15" s="1" t="inlineStr">
-        <is>
-          <t>L96: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: La re liure serr Ã© e peut causer de l'ombre ou de la</t>
-        </is>
-      </c>
-      <c r="K15" s="1" t="inlineStr">
-        <is>
-          <t>L109: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Comprend du matÃ©riel supplÃ©mentaire</t>
-        </is>
-      </c>
+      <c r="J15" s="1" t="inlineStr"/>
+      <c r="K15" s="1" t="inlineStr"/>
       <c r="L15" s="1" t="inlineStr"/>
       <c r="M15" s="1" t="inlineStr"/>
       <c r="N15" s="1" t="inlineStr"/>
@@ -1473,20 +1377,12 @@
       <c r="G16" s="1" t="inlineStr"/>
       <c r="H16" s="1" t="inlineStr">
         <is>
-          <t>L189: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER | suspicious token(s): 20X (letter/digit mix) :: 20X ã€�</t>
+          <t>L189: suspicious token(s): 20X (letter/digit mix) :: 20X 、</t>
         </is>
       </c>
       <c r="I16" s="1" t="inlineStr"/>
-      <c r="J16" s="1" t="inlineStr">
-        <is>
-          <t>L97: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: distorsion le long de la marge int Ã© rieure</t>
-        </is>
-      </c>
-      <c r="K16" s="1" t="inlineStr">
-        <is>
-          <t>L114: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: La reliure serrÃ©e peut causer de l'ombre ou de la</t>
-        </is>
-      </c>
+      <c r="J16" s="1" t="inlineStr"/>
+      <c r="K16" s="1" t="inlineStr"/>
       <c r="L16" s="1" t="inlineStr"/>
       <c r="M16" s="1" t="inlineStr"/>
       <c r="N16" s="1" t="inlineStr"/>
@@ -1532,16 +1428,8 @@
         </is>
       </c>
       <c r="I17" s="1" t="inlineStr"/>
-      <c r="J17" s="1" t="inlineStr">
-        <is>
-          <t>L106: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Il se peut que certaines pages blanches ajout Ã© es</t>
-        </is>
-      </c>
-      <c r="K17" s="1" t="inlineStr">
-        <is>
-          <t>L115: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: distorsion le long de la marge intÃ©rieure</t>
-        </is>
-      </c>
+      <c r="J17" s="1" t="inlineStr"/>
+      <c r="K17" s="1" t="inlineStr"/>
       <c r="L17" s="1" t="inlineStr"/>
       <c r="M17" s="1" t="inlineStr"/>
       <c r="N17" s="1" t="inlineStr"/>
@@ -1571,16 +1459,8 @@
         </is>
       </c>
       <c r="I18" s="1" t="inlineStr"/>
-      <c r="J18" s="1" t="inlineStr">
-        <is>
-          <t>L107: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: etc. ont et Ã© film Ã© es a nouveau de fa a</t>
-        </is>
-      </c>
-      <c r="K18" s="1" t="inlineStr">
-        <is>
-          <t>L118: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Seule Ã©dition disponible</t>
-        </is>
-      </c>
+      <c r="J18" s="1" t="inlineStr"/>
+      <c r="K18" s="1" t="inlineStr"/>
       <c r="L18" s="1" t="inlineStr"/>
       <c r="M18" s="1" t="inlineStr"/>
       <c r="N18" s="1" t="inlineStr"/>
@@ -1610,16 +1490,8 @@
         </is>
       </c>
       <c r="I19" s="1" t="inlineStr"/>
-      <c r="J19" s="1" t="inlineStr">
-        <is>
-          <t>L110: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: mais, lorsque cela Ã© tait possible. ces pages n'ont</t>
-        </is>
-      </c>
-      <c r="K19" s="1" t="inlineStr">
-        <is>
-          <t>L122: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="J19" s="1" t="inlineStr"/>
+      <c r="K19" s="1" t="inlineStr"/>
       <c r="L19" s="1" t="inlineStr"/>
       <c r="M19" s="1" t="inlineStr"/>
       <c r="N19" s="1" t="inlineStr"/>
@@ -1649,16 +1521,8 @@
         </is>
       </c>
       <c r="I20" s="1" t="inlineStr"/>
-      <c r="J20" s="1" t="inlineStr">
-        <is>
-          <t>L111: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: pas et Ã© film Ã© es.</t>
-        </is>
-      </c>
-      <c r="K20" s="1" t="inlineStr">
-        <is>
-          <t>L131: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: etc., ont Ã©tÃ© filmÃ©es Ã nouveau de faÃ§on Ã</t>
-        </is>
-      </c>
+      <c r="J20" s="1" t="inlineStr"/>
+      <c r="K20" s="1" t="inlineStr"/>
       <c r="L20" s="1" t="inlineStr"/>
       <c r="M20" s="1" t="inlineStr"/>
       <c r="N20" s="1" t="inlineStr"/>
@@ -1688,16 +1552,8 @@
         </is>
       </c>
       <c r="I21" s="1" t="inlineStr"/>
-      <c r="J21" s="1" t="inlineStr">
-        <is>
-          <t>L116: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: qu'il lui a Ã© te possible de se procurer. Les d Ã© tails</t>
-        </is>
-      </c>
-      <c r="K21" s="1" t="inlineStr">
-        <is>
-          <t>L138: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: II se peut que certaines pages blanches ajoutÃ©es</t>
-        </is>
-      </c>
+      <c r="J21" s="1" t="inlineStr"/>
+      <c r="K21" s="1" t="inlineStr"/>
       <c r="L21" s="1" t="inlineStr"/>
       <c r="M21" s="1" t="inlineStr"/>
       <c r="N21" s="1" t="inlineStr"/>
@@ -1723,20 +1579,12 @@
       <c r="G22" s="1" t="inlineStr"/>
       <c r="H22" s="1" t="inlineStr">
         <is>
-          <t>L197: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER | suspicious token(s): 20X (letter/digit mix) :: 20X ã€�</t>
+          <t>L197: suspicious token(s): 20X (letter/digit mix) :: 20X 、</t>
         </is>
       </c>
       <c r="I22" s="1" t="inlineStr"/>
-      <c r="J22" s="1" t="inlineStr">
-        <is>
-          <t>L118: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: de cet exemplaire qui sont peut- Ã¨ tre uniques du</t>
-        </is>
-      </c>
-      <c r="K22" s="1" t="inlineStr">
-        <is>
-          <t>L140: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: mais, lorsque cela Ã©tait possible, cas pages nâ€™ont</t>
-        </is>
-      </c>
+      <c r="J22" s="1" t="inlineStr"/>
+      <c r="K22" s="1" t="inlineStr"/>
       <c r="L22" s="1" t="inlineStr"/>
       <c r="M22" s="1" t="inlineStr"/>
       <c r="N22" s="1" t="inlineStr"/>
@@ -1766,16 +1614,8 @@
         </is>
       </c>
       <c r="I23" s="1" t="inlineStr"/>
-      <c r="J23" s="1" t="inlineStr">
-        <is>
-          <t>L133: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Qualit Ã© in Ã© gale de I'impression</t>
-        </is>
-      </c>
-      <c r="K23" s="1" t="inlineStr">
-        <is>
-          <t>L142: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: pas Ã©tÃ© filmÃ©es.</t>
-        </is>
-      </c>
+      <c r="J23" s="1" t="inlineStr"/>
+      <c r="K23" s="1" t="inlineStr"/>
       <c r="L23" s="1" t="inlineStr"/>
       <c r="M23" s="1" t="inlineStr"/>
       <c r="N23" s="1" t="inlineStr"/>
@@ -1805,16 +1645,8 @@
         </is>
       </c>
       <c r="I24" s="1" t="inlineStr"/>
-      <c r="J24" s="1" t="inlineStr">
-        <is>
-          <t>L136: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Reli Ã© avec d'autres documents</t>
-        </is>
-      </c>
-      <c r="K24" s="1" t="inlineStr">
-        <is>
-          <t>L148: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Commentaires supplÃ©mentaires;</t>
-        </is>
-      </c>
+      <c r="J24" s="1" t="inlineStr"/>
+      <c r="K24" s="1" t="inlineStr"/>
       <c r="L24" s="1" t="inlineStr"/>
       <c r="M24" s="1" t="inlineStr"/>
       <c r="N24" s="1" t="inlineStr"/>
@@ -1844,16 +1676,8 @@
         </is>
       </c>
       <c r="I25" s="1" t="inlineStr"/>
-      <c r="J25" s="1" t="inlineStr">
-        <is>
-          <t>L137: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Comprend du mat Ã© brie suppl Ã© mentaire</t>
-        </is>
-      </c>
-      <c r="K25" s="1" t="inlineStr">
-        <is>
-          <t>L153: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Ce document est filmÃ© au taux de rÃ©duction indiquÃ© ci-dessous.</t>
-        </is>
-      </c>
+      <c r="J25" s="1" t="inlineStr"/>
+      <c r="K25" s="1" t="inlineStr"/>
       <c r="L25" s="1" t="inlineStr"/>
       <c r="M25" s="1" t="inlineStr"/>
       <c r="N25" s="1" t="inlineStr"/>
@@ -1869,506 +1693,6 @@
       <c r="X25" s="1" t="inlineStr"/>
       <c r="Y25" s="1" t="inlineStr"/>
     </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr"/>
-      <c r="B26" s="1" t="inlineStr"/>
-      <c r="C26" s="1" t="inlineStr"/>
-      <c r="D26" s="1" t="inlineStr"/>
-      <c r="E26" s="1" t="inlineStr"/>
-      <c r="F26" s="1" t="inlineStr"/>
-      <c r="G26" s="1" t="inlineStr"/>
-      <c r="H26" s="1" t="inlineStr"/>
-      <c r="I26" s="1" t="inlineStr"/>
-      <c r="J26" s="1" t="inlineStr">
-        <is>
-          <t>L142: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Seule Ã© dition disponible</t>
-        </is>
-      </c>
-      <c r="K26" s="1" t="inlineStr">
-        <is>
-          <t>L169: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
-      <c r="L26" s="1" t="inlineStr"/>
-      <c r="M26" s="1" t="inlineStr"/>
-      <c r="N26" s="1" t="inlineStr"/>
-      <c r="O26" s="1" t="inlineStr"/>
-      <c r="P26" s="1" t="inlineStr"/>
-      <c r="Q26" s="1" t="inlineStr"/>
-      <c r="R26" s="1" t="inlineStr"/>
-      <c r="S26" s="1" t="inlineStr"/>
-      <c r="T26" s="1" t="inlineStr"/>
-      <c r="U26" s="1" t="inlineStr"/>
-      <c r="V26" s="1" t="inlineStr"/>
-      <c r="W26" s="1" t="inlineStr"/>
-      <c r="X26" s="1" t="inlineStr"/>
-      <c r="Y26" s="1" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr"/>
-      <c r="B27" s="1" t="inlineStr"/>
-      <c r="C27" s="1" t="inlineStr"/>
-      <c r="D27" s="1" t="inlineStr"/>
-      <c r="E27" s="1" t="inlineStr"/>
-      <c r="F27" s="1" t="inlineStr"/>
-      <c r="G27" s="1" t="inlineStr"/>
-      <c r="H27" s="1" t="inlineStr"/>
-      <c r="I27" s="1" t="inlineStr"/>
-      <c r="J27" s="1" t="inlineStr">
-        <is>
-          <t>L143: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: La re liure serr Ã© e peut causer de l'ombre ou de la</t>
-        </is>
-      </c>
-      <c r="K27" s="1" t="inlineStr"/>
-      <c r="L27" s="1" t="inlineStr"/>
-      <c r="M27" s="1" t="inlineStr"/>
-      <c r="N27" s="1" t="inlineStr"/>
-      <c r="O27" s="1" t="inlineStr"/>
-      <c r="P27" s="1" t="inlineStr"/>
-      <c r="Q27" s="1" t="inlineStr"/>
-      <c r="R27" s="1" t="inlineStr"/>
-      <c r="S27" s="1" t="inlineStr"/>
-      <c r="T27" s="1" t="inlineStr"/>
-      <c r="U27" s="1" t="inlineStr"/>
-      <c r="V27" s="1" t="inlineStr"/>
-      <c r="W27" s="1" t="inlineStr"/>
-      <c r="X27" s="1" t="inlineStr"/>
-      <c r="Y27" s="1" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr"/>
-      <c r="B28" s="1" t="inlineStr"/>
-      <c r="C28" s="1" t="inlineStr"/>
-      <c r="D28" s="1" t="inlineStr"/>
-      <c r="E28" s="1" t="inlineStr"/>
-      <c r="F28" s="1" t="inlineStr"/>
-      <c r="G28" s="1" t="inlineStr"/>
-      <c r="H28" s="1" t="inlineStr"/>
-      <c r="I28" s="1" t="inlineStr"/>
-      <c r="J28" s="1" t="inlineStr">
-        <is>
-          <t>L144: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: distorsion le long de la marge int Ã© rieure</t>
-        </is>
-      </c>
-      <c r="K28" s="1" t="inlineStr"/>
-      <c r="L28" s="1" t="inlineStr"/>
-      <c r="M28" s="1" t="inlineStr"/>
-      <c r="N28" s="1" t="inlineStr"/>
-      <c r="O28" s="1" t="inlineStr"/>
-      <c r="P28" s="1" t="inlineStr"/>
-      <c r="Q28" s="1" t="inlineStr"/>
-      <c r="R28" s="1" t="inlineStr"/>
-      <c r="S28" s="1" t="inlineStr"/>
-      <c r="T28" s="1" t="inlineStr"/>
-      <c r="U28" s="1" t="inlineStr"/>
-      <c r="V28" s="1" t="inlineStr"/>
-      <c r="W28" s="1" t="inlineStr"/>
-      <c r="X28" s="1" t="inlineStr"/>
-      <c r="Y28" s="1" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="inlineStr"/>
-      <c r="B29" s="1" t="inlineStr"/>
-      <c r="C29" s="1" t="inlineStr"/>
-      <c r="D29" s="1" t="inlineStr"/>
-      <c r="E29" s="1" t="inlineStr"/>
-      <c r="F29" s="1" t="inlineStr"/>
-      <c r="G29" s="1" t="inlineStr"/>
-      <c r="H29" s="1" t="inlineStr"/>
-      <c r="I29" s="1" t="inlineStr"/>
-      <c r="J29" s="1" t="inlineStr">
-        <is>
-          <t>L153: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Il se peut que certaines pages blanches ajout Ã© es</t>
-        </is>
-      </c>
-      <c r="K29" s="1" t="inlineStr"/>
-      <c r="L29" s="1" t="inlineStr"/>
-      <c r="M29" s="1" t="inlineStr"/>
-      <c r="N29" s="1" t="inlineStr"/>
-      <c r="O29" s="1" t="inlineStr"/>
-      <c r="P29" s="1" t="inlineStr"/>
-      <c r="Q29" s="1" t="inlineStr"/>
-      <c r="R29" s="1" t="inlineStr"/>
-      <c r="S29" s="1" t="inlineStr"/>
-      <c r="T29" s="1" t="inlineStr"/>
-      <c r="U29" s="1" t="inlineStr"/>
-      <c r="V29" s="1" t="inlineStr"/>
-      <c r="W29" s="1" t="inlineStr"/>
-      <c r="X29" s="1" t="inlineStr"/>
-      <c r="Y29" s="1" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr"/>
-      <c r="B30" s="1" t="inlineStr"/>
-      <c r="C30" s="1" t="inlineStr"/>
-      <c r="D30" s="1" t="inlineStr"/>
-      <c r="E30" s="1" t="inlineStr"/>
-      <c r="F30" s="1" t="inlineStr"/>
-      <c r="G30" s="1" t="inlineStr"/>
-      <c r="H30" s="1" t="inlineStr"/>
-      <c r="I30" s="1" t="inlineStr"/>
-      <c r="J30" s="1" t="inlineStr">
-        <is>
-          <t>L154: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: etc. ont et Ã© film Ã© es a nouveau de fa a</t>
-        </is>
-      </c>
-      <c r="K30" s="1" t="inlineStr"/>
-      <c r="L30" s="1" t="inlineStr"/>
-      <c r="M30" s="1" t="inlineStr"/>
-      <c r="N30" s="1" t="inlineStr"/>
-      <c r="O30" s="1" t="inlineStr"/>
-      <c r="P30" s="1" t="inlineStr"/>
-      <c r="Q30" s="1" t="inlineStr"/>
-      <c r="R30" s="1" t="inlineStr"/>
-      <c r="S30" s="1" t="inlineStr"/>
-      <c r="T30" s="1" t="inlineStr"/>
-      <c r="U30" s="1" t="inlineStr"/>
-      <c r="V30" s="1" t="inlineStr"/>
-      <c r="W30" s="1" t="inlineStr"/>
-      <c r="X30" s="1" t="inlineStr"/>
-      <c r="Y30" s="1" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr"/>
-      <c r="B31" s="1" t="inlineStr"/>
-      <c r="C31" s="1" t="inlineStr"/>
-      <c r="D31" s="1" t="inlineStr"/>
-      <c r="E31" s="1" t="inlineStr"/>
-      <c r="F31" s="1" t="inlineStr"/>
-      <c r="G31" s="1" t="inlineStr"/>
-      <c r="H31" s="1" t="inlineStr"/>
-      <c r="I31" s="1" t="inlineStr"/>
-      <c r="J31" s="1" t="inlineStr">
-        <is>
-          <t>L157: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: mais, lorsque cela Ã© tait possible. ces pages n'ont</t>
-        </is>
-      </c>
-      <c r="K31" s="1" t="inlineStr"/>
-      <c r="L31" s="1" t="inlineStr"/>
-      <c r="M31" s="1" t="inlineStr"/>
-      <c r="N31" s="1" t="inlineStr"/>
-      <c r="O31" s="1" t="inlineStr"/>
-      <c r="P31" s="1" t="inlineStr"/>
-      <c r="Q31" s="1" t="inlineStr"/>
-      <c r="R31" s="1" t="inlineStr"/>
-      <c r="S31" s="1" t="inlineStr"/>
-      <c r="T31" s="1" t="inlineStr"/>
-      <c r="U31" s="1" t="inlineStr"/>
-      <c r="V31" s="1" t="inlineStr"/>
-      <c r="W31" s="1" t="inlineStr"/>
-      <c r="X31" s="1" t="inlineStr"/>
-      <c r="Y31" s="1" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="inlineStr"/>
-      <c r="B32" s="1" t="inlineStr"/>
-      <c r="C32" s="1" t="inlineStr"/>
-      <c r="D32" s="1" t="inlineStr"/>
-      <c r="E32" s="1" t="inlineStr"/>
-      <c r="F32" s="1" t="inlineStr"/>
-      <c r="G32" s="1" t="inlineStr"/>
-      <c r="H32" s="1" t="inlineStr"/>
-      <c r="I32" s="1" t="inlineStr"/>
-      <c r="J32" s="1" t="inlineStr">
-        <is>
-          <t>L158: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: pas et Ã© film Ã© es.</t>
-        </is>
-      </c>
-      <c r="K32" s="1" t="inlineStr"/>
-      <c r="L32" s="1" t="inlineStr"/>
-      <c r="M32" s="1" t="inlineStr"/>
-      <c r="N32" s="1" t="inlineStr"/>
-      <c r="O32" s="1" t="inlineStr"/>
-      <c r="P32" s="1" t="inlineStr"/>
-      <c r="Q32" s="1" t="inlineStr"/>
-      <c r="R32" s="1" t="inlineStr"/>
-      <c r="S32" s="1" t="inlineStr"/>
-      <c r="T32" s="1" t="inlineStr"/>
-      <c r="U32" s="1" t="inlineStr"/>
-      <c r="V32" s="1" t="inlineStr"/>
-      <c r="W32" s="1" t="inlineStr"/>
-      <c r="X32" s="1" t="inlineStr"/>
-      <c r="Y32" s="1" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="1" t="inlineStr"/>
-      <c r="B33" s="1" t="inlineStr"/>
-      <c r="C33" s="1" t="inlineStr"/>
-      <c r="D33" s="1" t="inlineStr"/>
-      <c r="E33" s="1" t="inlineStr"/>
-      <c r="F33" s="1" t="inlineStr"/>
-      <c r="G33" s="1" t="inlineStr"/>
-      <c r="H33" s="1" t="inlineStr"/>
-      <c r="I33" s="1" t="inlineStr"/>
-      <c r="J33" s="1" t="inlineStr">
-        <is>
-          <t>L160: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Commentaires suppl Ã© mentaires:</t>
-        </is>
-      </c>
-      <c r="K33" s="1" t="inlineStr"/>
-      <c r="L33" s="1" t="inlineStr"/>
-      <c r="M33" s="1" t="inlineStr"/>
-      <c r="N33" s="1" t="inlineStr"/>
-      <c r="O33" s="1" t="inlineStr"/>
-      <c r="P33" s="1" t="inlineStr"/>
-      <c r="Q33" s="1" t="inlineStr"/>
-      <c r="R33" s="1" t="inlineStr"/>
-      <c r="S33" s="1" t="inlineStr"/>
-      <c r="T33" s="1" t="inlineStr"/>
-      <c r="U33" s="1" t="inlineStr"/>
-      <c r="V33" s="1" t="inlineStr"/>
-      <c r="W33" s="1" t="inlineStr"/>
-      <c r="X33" s="1" t="inlineStr"/>
-      <c r="Y33" s="1" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="inlineStr"/>
-      <c r="B34" s="1" t="inlineStr"/>
-      <c r="C34" s="1" t="inlineStr"/>
-      <c r="D34" s="1" t="inlineStr"/>
-      <c r="E34" s="1" t="inlineStr"/>
-      <c r="F34" s="1" t="inlineStr"/>
-      <c r="G34" s="1" t="inlineStr"/>
-      <c r="H34" s="1" t="inlineStr"/>
-      <c r="I34" s="1" t="inlineStr"/>
-      <c r="J34" s="1" t="inlineStr">
-        <is>
-          <t>L162: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Commentaires suppl Ã© mentaires:</t>
-        </is>
-      </c>
-      <c r="K34" s="1" t="inlineStr"/>
-      <c r="L34" s="1" t="inlineStr"/>
-      <c r="M34" s="1" t="inlineStr"/>
-      <c r="N34" s="1" t="inlineStr"/>
-      <c r="O34" s="1" t="inlineStr"/>
-      <c r="P34" s="1" t="inlineStr"/>
-      <c r="Q34" s="1" t="inlineStr"/>
-      <c r="R34" s="1" t="inlineStr"/>
-      <c r="S34" s="1" t="inlineStr"/>
-      <c r="T34" s="1" t="inlineStr"/>
-      <c r="U34" s="1" t="inlineStr"/>
-      <c r="V34" s="1" t="inlineStr"/>
-      <c r="W34" s="1" t="inlineStr"/>
-      <c r="X34" s="1" t="inlineStr"/>
-      <c r="Y34" s="1" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="inlineStr"/>
-      <c r="B35" s="1" t="inlineStr"/>
-      <c r="C35" s="1" t="inlineStr"/>
-      <c r="D35" s="1" t="inlineStr"/>
-      <c r="E35" s="1" t="inlineStr"/>
-      <c r="F35" s="1" t="inlineStr"/>
-      <c r="G35" s="1" t="inlineStr"/>
-      <c r="H35" s="1" t="inlineStr"/>
-      <c r="I35" s="1" t="inlineStr"/>
-      <c r="J35" s="1" t="inlineStr">
-        <is>
-          <t>L174: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Couverture restaur Ã© e et / ou pellicul Ã© e</t>
-        </is>
-      </c>
-      <c r="K35" s="1" t="inlineStr"/>
-      <c r="L35" s="1" t="inlineStr"/>
-      <c r="M35" s="1" t="inlineStr"/>
-      <c r="N35" s="1" t="inlineStr"/>
-      <c r="O35" s="1" t="inlineStr"/>
-      <c r="P35" s="1" t="inlineStr"/>
-      <c r="Q35" s="1" t="inlineStr"/>
-      <c r="R35" s="1" t="inlineStr"/>
-      <c r="S35" s="1" t="inlineStr"/>
-      <c r="T35" s="1" t="inlineStr"/>
-      <c r="U35" s="1" t="inlineStr"/>
-      <c r="V35" s="1" t="inlineStr"/>
-      <c r="W35" s="1" t="inlineStr"/>
-      <c r="X35" s="1" t="inlineStr"/>
-      <c r="Y35" s="1" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="inlineStr"/>
-      <c r="B36" s="1" t="inlineStr"/>
-      <c r="C36" s="1" t="inlineStr"/>
-      <c r="D36" s="1" t="inlineStr"/>
-      <c r="E36" s="1" t="inlineStr"/>
-      <c r="F36" s="1" t="inlineStr"/>
-      <c r="G36" s="1" t="inlineStr"/>
-      <c r="H36" s="1" t="inlineStr"/>
-      <c r="I36" s="1" t="inlineStr"/>
-      <c r="J36" s="1" t="inlineStr">
-        <is>
-          <t>L175: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Pages restaur Ã© es et / ou pellicul Ã© es</t>
-        </is>
-      </c>
-      <c r="K36" s="1" t="inlineStr"/>
-      <c r="L36" s="1" t="inlineStr"/>
-      <c r="M36" s="1" t="inlineStr"/>
-      <c r="N36" s="1" t="inlineStr"/>
-      <c r="O36" s="1" t="inlineStr"/>
-      <c r="P36" s="1" t="inlineStr"/>
-      <c r="Q36" s="1" t="inlineStr"/>
-      <c r="R36" s="1" t="inlineStr"/>
-      <c r="S36" s="1" t="inlineStr"/>
-      <c r="T36" s="1" t="inlineStr"/>
-      <c r="U36" s="1" t="inlineStr"/>
-      <c r="V36" s="1" t="inlineStr"/>
-      <c r="W36" s="1" t="inlineStr"/>
-      <c r="X36" s="1" t="inlineStr"/>
-      <c r="Y36" s="1" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="inlineStr"/>
-      <c r="B37" s="1" t="inlineStr"/>
-      <c r="C37" s="1" t="inlineStr"/>
-      <c r="D37" s="1" t="inlineStr"/>
-      <c r="E37" s="1" t="inlineStr"/>
-      <c r="F37" s="1" t="inlineStr"/>
-      <c r="G37" s="1" t="inlineStr"/>
-      <c r="H37" s="1" t="inlineStr"/>
-      <c r="I37" s="1" t="inlineStr"/>
-      <c r="J37" s="1" t="inlineStr">
-        <is>
-          <t>L180: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Pages d Ã© scolor Ã© es, tachet Ã© es ou piqu Ã© es</t>
-        </is>
-      </c>
-      <c r="K37" s="1" t="inlineStr"/>
-      <c r="L37" s="1" t="inlineStr"/>
-      <c r="M37" s="1" t="inlineStr"/>
-      <c r="N37" s="1" t="inlineStr"/>
-      <c r="O37" s="1" t="inlineStr"/>
-      <c r="P37" s="1" t="inlineStr"/>
-      <c r="Q37" s="1" t="inlineStr"/>
-      <c r="R37" s="1" t="inlineStr"/>
-      <c r="S37" s="1" t="inlineStr"/>
-      <c r="T37" s="1" t="inlineStr"/>
-      <c r="U37" s="1" t="inlineStr"/>
-      <c r="V37" s="1" t="inlineStr"/>
-      <c r="W37" s="1" t="inlineStr"/>
-      <c r="X37" s="1" t="inlineStr"/>
-      <c r="Y37" s="1" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="inlineStr"/>
-      <c r="B38" s="1" t="inlineStr"/>
-      <c r="C38" s="1" t="inlineStr"/>
-      <c r="D38" s="1" t="inlineStr"/>
-      <c r="E38" s="1" t="inlineStr"/>
-      <c r="F38" s="1" t="inlineStr"/>
-      <c r="G38" s="1" t="inlineStr"/>
-      <c r="H38" s="1" t="inlineStr"/>
-      <c r="I38" s="1" t="inlineStr"/>
-      <c r="J38" s="1" t="inlineStr">
-        <is>
-          <t>L183: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Cartes g Ã© ographiques en couleur</t>
-        </is>
-      </c>
-      <c r="K38" s="1" t="inlineStr"/>
-      <c r="L38" s="1" t="inlineStr"/>
-      <c r="M38" s="1" t="inlineStr"/>
-      <c r="N38" s="1" t="inlineStr"/>
-      <c r="O38" s="1" t="inlineStr"/>
-      <c r="P38" s="1" t="inlineStr"/>
-      <c r="Q38" s="1" t="inlineStr"/>
-      <c r="R38" s="1" t="inlineStr"/>
-      <c r="S38" s="1" t="inlineStr"/>
-      <c r="T38" s="1" t="inlineStr"/>
-      <c r="U38" s="1" t="inlineStr"/>
-      <c r="V38" s="1" t="inlineStr"/>
-      <c r="W38" s="1" t="inlineStr"/>
-      <c r="X38" s="1" t="inlineStr"/>
-      <c r="Y38" s="1" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="inlineStr"/>
-      <c r="B39" s="1" t="inlineStr"/>
-      <c r="C39" s="1" t="inlineStr"/>
-      <c r="D39" s="1" t="inlineStr"/>
-      <c r="E39" s="1" t="inlineStr"/>
-      <c r="F39" s="1" t="inlineStr"/>
-      <c r="G39" s="1" t="inlineStr"/>
-      <c r="H39" s="1" t="inlineStr"/>
-      <c r="I39" s="1" t="inlineStr"/>
-      <c r="J39" s="1" t="inlineStr">
-        <is>
-          <t>L184: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Pages d Ã© tach Ã© es</t>
-        </is>
-      </c>
-      <c r="K39" s="1" t="inlineStr"/>
-      <c r="L39" s="1" t="inlineStr"/>
-      <c r="M39" s="1" t="inlineStr"/>
-      <c r="N39" s="1" t="inlineStr"/>
-      <c r="O39" s="1" t="inlineStr"/>
-      <c r="P39" s="1" t="inlineStr"/>
-      <c r="Q39" s="1" t="inlineStr"/>
-      <c r="R39" s="1" t="inlineStr"/>
-      <c r="S39" s="1" t="inlineStr"/>
-      <c r="T39" s="1" t="inlineStr"/>
-      <c r="U39" s="1" t="inlineStr"/>
-      <c r="V39" s="1" t="inlineStr"/>
-      <c r="W39" s="1" t="inlineStr"/>
-      <c r="X39" s="1" t="inlineStr"/>
-      <c r="Y39" s="1" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="inlineStr"/>
-      <c r="B40" s="1" t="inlineStr"/>
-      <c r="C40" s="1" t="inlineStr"/>
-      <c r="D40" s="1" t="inlineStr"/>
-      <c r="E40" s="1" t="inlineStr"/>
-      <c r="F40" s="1" t="inlineStr"/>
-      <c r="G40" s="1" t="inlineStr"/>
-      <c r="H40" s="1" t="inlineStr"/>
-      <c r="I40" s="1" t="inlineStr"/>
-      <c r="J40" s="1" t="inlineStr">
-        <is>
-          <t>L189: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER | suspicious token(s): 20X (letter/digit mix) :: 20X ã€�</t>
-        </is>
-      </c>
-      <c r="K40" s="1" t="inlineStr"/>
-      <c r="L40" s="1" t="inlineStr"/>
-      <c r="M40" s="1" t="inlineStr"/>
-      <c r="N40" s="1" t="inlineStr"/>
-      <c r="O40" s="1" t="inlineStr"/>
-      <c r="P40" s="1" t="inlineStr"/>
-      <c r="Q40" s="1" t="inlineStr"/>
-      <c r="R40" s="1" t="inlineStr"/>
-      <c r="S40" s="1" t="inlineStr"/>
-      <c r="T40" s="1" t="inlineStr"/>
-      <c r="U40" s="1" t="inlineStr"/>
-      <c r="V40" s="1" t="inlineStr"/>
-      <c r="W40" s="1" t="inlineStr"/>
-      <c r="X40" s="1" t="inlineStr"/>
-      <c r="Y40" s="1" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="inlineStr"/>
-      <c r="B41" s="1" t="inlineStr"/>
-      <c r="C41" s="1" t="inlineStr"/>
-      <c r="D41" s="1" t="inlineStr"/>
-      <c r="E41" s="1" t="inlineStr"/>
-      <c r="F41" s="1" t="inlineStr"/>
-      <c r="G41" s="1" t="inlineStr"/>
-      <c r="H41" s="1" t="inlineStr"/>
-      <c r="I41" s="1" t="inlineStr"/>
-      <c r="J41" s="1" t="inlineStr">
-        <is>
-          <t>L197: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER | suspicious token(s): 20X (letter/digit mix) :: 20X ã€�</t>
-        </is>
-      </c>
-      <c r="K41" s="1" t="inlineStr"/>
-      <c r="L41" s="1" t="inlineStr"/>
-      <c r="M41" s="1" t="inlineStr"/>
-      <c r="N41" s="1" t="inlineStr"/>
-      <c r="O41" s="1" t="inlineStr"/>
-      <c r="P41" s="1" t="inlineStr"/>
-      <c r="Q41" s="1" t="inlineStr"/>
-      <c r="R41" s="1" t="inlineStr"/>
-      <c r="S41" s="1" t="inlineStr"/>
-      <c r="T41" s="1" t="inlineStr"/>
-      <c r="U41" s="1" t="inlineStr"/>
-      <c r="V41" s="1" t="inlineStr"/>
-      <c r="W41" s="1" t="inlineStr"/>
-      <c r="X41" s="1" t="inlineStr"/>
-      <c r="Y41" s="1" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
